--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_227_R23.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_227_R23.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.247</v>
+        <v>6.3656</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1732</v>
+        <v>6.5271</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0738</v>
+        <v>-0.1614</v>
       </c>
       <c r="G2" t="n">
         <v>6.297</v>
@@ -610,13 +610,13 @@
         <v>0.6959</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3264</v>
+        <v>0.445</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2987</v>
+        <v>0.0551</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6251</v>
+        <v>0.3899</v>
       </c>
       <c r="V2" t="n">
         <v>-1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5113</v>
+        <v>5.6971</v>
       </c>
       <c r="E3" t="n">
-        <v>2.66</v>
+        <v>3.0139</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8513</v>
+        <v>2.6832</v>
       </c>
       <c r="G3" t="n">
         <v>2.1884</v>
@@ -688,13 +688,13 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0883</v>
+        <v>0.2741</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5228</v>
+        <v>-0.1689</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6111</v>
+        <v>0.443</v>
       </c>
       <c r="V3" t="n">
         <v>2.5387</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3322</v>
+        <v>5.09</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8382</v>
+        <v>3.4279</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4941</v>
+        <v>1.6621</v>
       </c>
       <c r="G4" t="n">
         <v>4.986</v>
@@ -766,13 +766,13 @@
         <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4424</v>
+        <v>0.3154</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3734</v>
+        <v>0.2164</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>0.2525</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.1098</v>
+        <v>4.6989</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6745</v>
+        <v>3.0284</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4353</v>
+        <v>1.6705</v>
       </c>
       <c r="G5" t="n">
         <v>2.8758</v>
@@ -844,13 +844,13 @@
         <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1577</v>
+        <v>0.4314</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4481</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2904</v>
+        <v>0.5256</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3797</v>
+        <v>4.036</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6356</v>
+        <v>4.9894</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2559</v>
+        <v>-0.9534</v>
       </c>
       <c r="G6" t="n">
         <v>2.3224</v>
@@ -922,13 +922,13 @@
         <v>0.4639</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3369</v>
+        <v>0.3194</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.224</v>
+        <v>0.1298</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1129</v>
+        <v>0.1896</v>
       </c>
       <c r="V6" t="n">
         <v>0.9304</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4099</v>
+        <v>2.0304</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4638</v>
+        <v>2.5014</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.054</v>
+        <v>-0.471</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2997</v>
+        <v>2.2464</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2724</v>
+        <v>1.6073</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0273</v>
+        <v>0.6391</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2926</v>
+        <v>2.8429</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6301</v>
+        <v>1.2001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6625</v>
+        <v>1.6428</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0071</v>
+        <v>-0.5965</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3577</v>
+        <v>0.4071</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3648</v>
+        <v>-1.0037</v>
       </c>
       <c r="P7" t="n">
         <v>-1.6237</v>
@@ -1000,28 +1000,28 @@
         <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5225</v>
+        <v>0.8716</v>
       </c>
       <c r="T7" t="n">
-        <v>2.135</v>
+        <v>0.3697</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3875</v>
+        <v>0.5019</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7886</v>
+        <v>0.5361</v>
       </c>
       <c r="W7" t="n">
-        <v>1.3558</v>
+        <v>1.6083</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.3164</v>
+        <v>1.6257</v>
       </c>
       <c r="E8" t="n">
-        <v>2.6193</v>
+        <v>0.9129</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3029</v>
+        <v>0.7129</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2464</v>
+        <v>1.2581</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6073</v>
+        <v>-0.1271</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6391</v>
+        <v>1.3853</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8429</v>
+        <v>1.8837</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2001</v>
+        <v>0.7562</v>
       </c>
       <c r="L8" t="n">
-        <v>1.6428</v>
+        <v>1.1275</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5965</v>
+        <v>-0.6256</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4071</v>
+        <v>-0.8834</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0037</v>
+        <v>0.2578</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1576</v>
+        <v>0.744</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4876</v>
+        <v>0.1889</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.5551</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>-1.0722</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.7266</v>
+        <v>1.2697</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9129</v>
+        <v>-0.1898</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8137</v>
+        <v>1.4595</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2581</v>
+        <v>1.5585</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1271</v>
+        <v>0.6351</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3853</v>
+        <v>0.9234</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8837</v>
+        <v>1.2264</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7562</v>
+        <v>1.1932</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1275</v>
+        <v>0.0333</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6256</v>
+        <v>0.3321</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8834</v>
+        <v>-0.5581</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2578</v>
+        <v>0.8901</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R9" t="n">
         <v>1.8556</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8448</v>
+        <v>-0.2192</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1889</v>
+        <v>-0.1689</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6559</v>
+        <v>-0.0503</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0722</v>
+        <v>0.3943</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7678</v>
+        <v>1.0452</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4937</v>
+        <v>2.1664</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2741</v>
+        <v>-1.1212</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1348</v>
+        <v>2.2997</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0866</v>
+        <v>1.2724</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2213</v>
+        <v>1.0273</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3281</v>
+        <v>2.2926</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6288</v>
+        <v>1.6301</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6993</v>
+        <v>0.6625</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1933</v>
+        <v>0.0071</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7153</v>
+        <v>-0.3577</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5221</v>
+        <v>0.3648</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9278</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8443000000000001</v>
+        <v>1.1578</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4129</v>
+        <v>0.8375</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4314</v>
+        <v>0.3203</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2836</v>
+        <v>-0.7886</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0722</v>
+        <v>1.3558</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.3558</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6133999999999999</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5436</v>
+        <v>0.0219</v>
       </c>
       <c r="F11" t="n">
-        <v>1.157</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5585</v>
+        <v>1.1348</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6351</v>
+        <v>-0.0866</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9234</v>
+        <v>1.2213</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2264</v>
+        <v>1.3281</v>
       </c>
       <c r="K11" t="n">
-        <v>1.1932</v>
+        <v>0.6288</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0333</v>
+        <v>0.6993</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3321</v>
+        <v>-0.1933</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5581</v>
+        <v>-0.7153</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8901</v>
+        <v>0.5221</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4639</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q11" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8754999999999999</v>
+        <v>0.1709</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5228</v>
+        <v>-0.0589</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3528</v>
+        <v>0.2298</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3943</v>
+        <v>-0.2836</v>
       </c>
       <c r="W11" t="n">
         <v>1.0722</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3199</v>
+        <v>-0.741</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.253</v>
+        <v>-1.0787</v>
       </c>
       <c r="F12" t="n">
-        <v>0.573</v>
+        <v>0.3377</v>
       </c>
       <c r="G12" t="n">
         <v>0.1781</v>
@@ -1390,13 +1390,13 @@
         <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>1.9975</v>
+        <v>0.9366</v>
       </c>
       <c r="T12" t="n">
-        <v>1.274</v>
+        <v>0.4483</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7235</v>
+        <v>0.4883</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.2449</v>
+        <v>-2.723</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.4857</v>
+        <v>-1.1319</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7592</v>
+        <v>-1.5912</v>
       </c>
       <c r="G13" t="n">
         <v>-2.3591</v>
@@ -1468,13 +1468,13 @@
         <v>0.6959</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3677</v>
+        <v>0.1542</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2987</v>
+        <v>0.0551</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-1.214</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>28.4891</v>
+        <v>28.4889</v>
       </c>
       <c r="E14" t="n">
         <v>24.1889</v>
       </c>
       <c r="F14" t="n">
-        <v>4.3003</v>
+        <v>4.3001</v>
       </c>
       <c r="G14" t="n">
         <v>24.9861</v>
@@ -1552,16 +1552,16 @@
         <v>1.8099</v>
       </c>
       <c r="U14" t="n">
-        <v>3.7911</v>
+        <v>3.7914</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2214</v>
+        <v>0.2213999999999996</v>
       </c>
       <c r="W14" t="n">
         <v>8.466900000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.2455</v>
+        <v>-8.245500000000002</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.748</v>
+        <v>1.9167</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7547</v>
+        <v>3.9906</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.0067</v>
+        <v>-2.0739</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1275</v>
@@ -1624,13 +1624,13 @@
         <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7328</v>
+        <v>-0.5641</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8057</v>
+        <v>-0.5698</v>
       </c>
       <c r="U15" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0057</v>
       </c>
       <c r="V15" t="n">
         <v>2.1444</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5247</v>
+        <v>1.7435</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3193</v>
+        <v>1.4373</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2054</v>
+        <v>0.3062</v>
       </c>
       <c r="G16" t="n">
         <v>1.6275</v>
@@ -1702,13 +1702,13 @@
         <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5461</v>
+        <v>-0.3273</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1415</v>
+        <v>-0.0235</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4046</v>
+        <v>-0.3038</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2525</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2818</v>
+        <v>1.0623</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8626</v>
+        <v>2.5088</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5809</v>
+        <v>-1.4465</v>
       </c>
       <c r="G17" t="n">
         <v>0.8539</v>
@@ -1780,13 +1780,13 @@
         <v>0.6959</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.268</v>
+        <v>-0.4874</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1142</v>
+        <v>-0.2396</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3822</v>
+        <v>-0.2478</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4667</v>
+        <v>-0.6449</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8845</v>
+        <v>-0.0591</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4177</v>
+        <v>-0.5858</v>
       </c>
       <c r="G18" t="n">
         <v>-0.592</v>
@@ -1858,13 +1858,13 @@
         <v>1.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0794</v>
+        <v>-0.0323</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6018</v>
+        <v>-0.3418</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4775</v>
+        <v>0.3095</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2525</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2006</v>
+        <v>-1.2171</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1612</v>
+        <v>-0.0433</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0394</v>
+        <v>-1.1739</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8661</v>
@@ -1936,13 +1936,13 @@
         <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4042</v>
+        <v>-0.4206</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3734</v>
+        <v>-0.2555</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0307</v>
+        <v>-0.1652</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3943</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. BOOKER</t>
+          <t>L. BROWN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6721</v>
+        <v>-2.4003</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1578</v>
+        <v>-1.7219</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.8299</v>
+        <v>-0.6784</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.0207</v>
+        <v>-2.9065</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4176</v>
+        <v>-2.1837</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.6031</v>
+        <v>-0.7228</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3046</v>
+        <v>-1.548</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7023</v>
+        <v>-1.3003</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.2477</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.7161</v>
+        <v>-1.3584</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7153</v>
+        <v>-0.8834</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.0008</v>
+        <v>-0.4751</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2996</v>
+        <v>-0.3341</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4288</v>
+        <v>-0.0863</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1291</v>
+        <v>-0.2478</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1107</v>
+        <v>1.0722</v>
       </c>
       <c r="W20" t="n">
-        <v>2.0336</v>
+        <v>1.0722</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. BROWN</t>
+          <t>D. BOOKER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8886</v>
+        <v>-3.0425</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0758</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8128</v>
+        <v>-3.9643</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.9065</v>
+        <v>-4.0207</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.1837</v>
+        <v>-1.4176</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7228</v>
+        <v>-2.6031</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.548</v>
+        <v>-1.3046</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.3003</v>
+        <v>-0.7023</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.2477</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3584</v>
+        <v>-2.7161</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8834</v>
+        <v>-0.7153</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4751</v>
+        <v>-2.0008</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8224</v>
+        <v>-0.0707</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4402</v>
+        <v>0.1928</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3822</v>
+        <v>-0.2636</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0722</v>
+        <v>-0.1107</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0722</v>
+        <v>2.0336</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.9553</v>
+        <v>-5.3826</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0258</v>
+        <v>-3.554</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9295</v>
+        <v>-1.8286</v>
       </c>
       <c r="G22" t="n">
         <v>-7.3479</v>
@@ -2170,13 +2170,13 @@
         <v>2.3195</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3755</v>
+        <v>-0.8028</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0297</v>
+        <v>-0.5579</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3457</v>
+        <v>-0.2449</v>
       </c>
       <c r="V22" t="n">
         <v>1.6083</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.1397</v>
+        <v>-6.342</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2085</v>
+        <v>-0.0274</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.3481</v>
+        <v>-6.3145</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8252</v>
@@ -2248,13 +2248,13 @@
         <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6339</v>
+        <v>-0.8362000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5579</v>
+        <v>-0.7938</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.076</v>
+        <v>-0.0424</v>
       </c>
       <c r="V23" t="n">
         <v>-3.2166</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.686</v>
+        <v>-7.0728</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.1395</v>
+        <v>-4.2574</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.5465</v>
+        <v>-2.8154</v>
       </c>
       <c r="G24" t="n">
         <v>-3.8831</v>
@@ -2326,13 +2326,13 @@
         <v>1.6237</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4112</v>
+        <v>-0.798</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4086</v>
+        <v>-0.5265</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0026</v>
+        <v>-0.2715</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5361</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.968</v>
+        <v>-7.1094</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.1575</v>
+        <v>-4.5678</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.8105</v>
+        <v>-2.5417</v>
       </c>
       <c r="G25" t="n">
         <v>-5.8983</v>
@@ -2404,13 +2404,13 @@
         <v>2.3195</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.7862</v>
+        <v>-0.9276</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1791</v>
+        <v>-0.5893</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6071</v>
+        <v>-0.3383</v>
       </c>
       <c r="V25" t="n">
         <v>-0.2836</v>
@@ -2440,10 +2440,10 @@
         <v>-28.4891</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.372400000000001</v>
+        <v>-5.372299999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-23.1166</v>
+        <v>-23.1168</v>
       </c>
       <c r="G26" t="n">
         <v>-24.9859</v>
@@ -2455,13 +2455,13 @@
         <v>-13.3843</v>
       </c>
       <c r="J26" t="n">
-        <v>4.003100000000003</v>
+        <v>4.003100000000001</v>
       </c>
       <c r="K26" t="n">
         <v>2.3812</v>
       </c>
       <c r="L26" t="n">
-        <v>1.6217</v>
+        <v>1.621699999999999</v>
       </c>
       <c r="M26" t="n">
         <v>-28.9887</v>
@@ -2482,16 +2482,16 @@
         <v>15.077</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.6013</v>
+        <v>-5.6011</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.7913</v>
+        <v>-3.7912</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.8098</v>
+        <v>-1.8101</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.2213999999999995</v>
+        <v>-0.2214</v>
       </c>
       <c r="W26" t="n">
         <v>7.1732</v>
